--- a/outputs/tables/table_llms_merged_range.xlsx
+++ b/outputs/tables/table_llms_merged_range.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>Temp 0.5 With Knowledge (min - max) (NR / R)</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>All (NR / R)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +486,11 @@
           <t>0.64 (0.49 - 0.76) / 0.71 (0.55 - 0.83)</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.63 / 0.71</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,193 +518,233 @@
           <t>0.63 (0.44 - 0.83) / 0.72 (0.55 - 0.87)</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.62 / 0.71</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>deepseek-ai_DeepSeek-R1</t>
+          <t>claude-sonnet-4-5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.62 (0.43 - 0.79) / 0.69 (0.51 - 0.87)</t>
+          <t>0.57 (0.39 - 0.75) / 0.68 (0.53 - 0.85)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.37 (0.31 - 0.45) / 0.46 (0.41 - 0.55)</t>
+          <t>0.52 (0.39 - 0.65) / 0.62 (0.50 - 0.75)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.45 (0.23 - 0.75) / 0.54 (0.32 - 0.84)</t>
+          <t>0.56 (0.32 - 0.75) / 0.66 (0.43 - 0.85)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.37 (0.26 - 0.50) / 0.46 (0.37 - 0.60)</t>
+          <t>0.53 (0.40 - 0.64) / 0.63 (0.51 - 0.73)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.54 / 0.65</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-5</t>
+          <t>gemini-2.5-flash</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.57 (0.39 - 0.75) / 0.68 (0.53 - 0.85)</t>
+          <t>0.56 (0.39 - 0.72) / 0.67 (0.49 - 0.84)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.52 (0.39 - 0.65) / 0.62 (0.50 - 0.75)</t>
+          <t>0.53 (0.47 - 0.65) / 0.63 (0.55 - 0.74)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.56 (0.32 - 0.75) / 0.66 (0.43 - 0.85)</t>
+          <t>0.58 (0.35 - 0.77) / 0.66 (0.45 - 0.88)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.53 (0.40 - 0.64) / 0.63 (0.51 - 0.73)</t>
+          <t>0.53 (0.40 - 0.67) / 0.64 (0.50 - 0.75)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.55 / 0.65</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Qwen_Qwen3-Next-80B-A3B-Thinking</t>
+          <t>mistral-large-latest</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.59 (0.42 - 0.72) / 0.67 (0.49 - 0.83)</t>
+          <t>0.57 (0.38 - 0.73) / 0.67 (0.48 - 0.82)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.44 (0.38 - 0.47) / 0.54 (0.46 - 0.58)</t>
+          <t>0.51 (0.31 - 0.71) / 0.61 (0.43 - 0.77)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.58 (0.37 - 0.74) / 0.66 (0.44 - 0.84)</t>
+          <t>0.54 (0.25 - 0.75) / 0.64 (0.37 - 0.83)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.44 (0.37 - 0.50) / 0.54 (0.45 - 0.61)</t>
+          <t>0.49 (0.29 - 0.67) / 0.60 (0.41 - 0.75)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.53 / 0.63</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash</t>
+          <t>moonshotai_Kimi-K2-Thinking</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.56 (0.39 - 0.72) / 0.67 (0.49 - 0.84)</t>
+          <t>0.51 (0.38 - 0.70) / 0.59 (0.47 - 0.75)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.53 (0.47 - 0.65) / 0.63 (0.55 - 0.74)</t>
+          <t>0.52 (0.45 - 0.64) / 0.62 (0.55 - 0.74)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.58 (0.35 - 0.77) / 0.66 (0.45 - 0.88)</t>
+          <t>0.52 (0.16 - 0.78) / 0.60 (0.25 - 0.87)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.53 (0.40 - 0.67) / 0.64 (0.50 - 0.75)</t>
+          <t>0.56 (0.46 - 0.70) / 0.67 (0.56 - 0.80)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.53 / 0.62</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>moonshotai_Kimi-K2-Thinking</t>
+          <t>Qwen_Qwen3-Next-80B-A3B-Thinking</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.51 (0.38 - 0.70) / 0.59 (0.47 - 0.75)</t>
+          <t>0.59 (0.42 - 0.72) / 0.67 (0.49 - 0.83)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.52 (0.45 - 0.64) / 0.62 (0.55 - 0.74)</t>
+          <t>0.44 (0.38 - 0.47) / 0.54 (0.46 - 0.58)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.52 (0.16 - 0.78) / 0.60 (0.25 - 0.87)</t>
+          <t>0.58 (0.37 - 0.74) / 0.66 (0.44 - 0.84)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.56 (0.46 - 0.70) / 0.67 (0.56 - 0.80)</t>
+          <t>0.44 (0.37 - 0.50) / 0.54 (0.45 - 0.61)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.51 / 0.60</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistral-large-latest</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.57 (0.38 - 0.73) / 0.67 (0.48 - 0.82)</t>
+          <t>0.57 (0.35 - 0.70) / 0.65 (0.42 - 0.82)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.51 (0.31 - 0.71) / 0.61 (0.43 - 0.77)</t>
+          <t>0.38 (0.21 - 0.47) / 0.47 (0.30 - 0.60)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.54 (0.25 - 0.75) / 0.64 (0.37 - 0.83)</t>
+          <t>0.53 (0.28 - 0.73) / 0.61 (0.34 - 0.83)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.49 (0.29 - 0.67) / 0.60 (0.41 - 0.75)</t>
+          <t>0.42 (0.23 - 0.56) / 0.50 (0.30 - 0.66)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.47 / 0.56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gpt-4o-mini</t>
+          <t>deepseek-ai_DeepSeek-R1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.57 (0.35 - 0.70) / 0.65 (0.42 - 0.82)</t>
+          <t>0.62 (0.43 - 0.79) / 0.69 (0.51 - 0.87)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.38 (0.21 - 0.47) / 0.47 (0.30 - 0.60)</t>
+          <t>0.37 (0.31 - 0.45) / 0.46 (0.41 - 0.55)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.53 (0.28 - 0.73) / 0.61 (0.34 - 0.83)</t>
+          <t>0.45 (0.23 - 0.75) / 0.54 (0.32 - 0.84)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.42 (0.23 - 0.56) / 0.50 (0.30 - 0.66)</t>
+          <t>0.37 (0.26 - 0.50) / 0.46 (0.37 - 0.60)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.45 / 0.54</t>
         </is>
       </c>
     </row>
@@ -722,6 +772,11 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>0.42 (0.33 - 0.53) / 0.50 (0.41 - 0.60)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.33 / 0.40</t>
         </is>
       </c>
     </row>
